--- a/docs/requirements/CivicConnect_M1_Registers.xlsx
+++ b/docs/requirements/CivicConnect_M1_Registers.xlsx
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="981">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="984">
   <si>
     <t xml:space="preserve">CivicConnect - Milestone 1 controlled registers</t>
   </si>
@@ -3007,6 +3007,15 @@
   </si>
   <si>
     <t xml:space="preserve">The first attempt was rejected because it was not vector source that could be regenerated: the initial figure was a canvas rendering rather than SVG. It was redone as SVG generated from a Python script and rendered to PNG, so a marker can be moved by editing the source and re-rendering rather than by redrawing the image. Two discrepancies were then found on checking and are recorded rather than silently corrected. (1) Figure 1 names one gated decision per concern, but the Decision Log records FEC-01 and FEC-06 as gating DEC-009 as well as DEC-011, since DEC-009 requires the record-level authorisation shape from FEC-01 and the reporting load position from FEC-06; the figure understates those two rows by one decision. The Forward Considerations sheet also cites DEC-010 in the Links column for FEC-03 and FEC-05 but cites no decision for FEC-01 or FEC-06, so that link is recorded in the Decision Log only. (2) In Figure 2 the single New to In Progress arc carries two stacked labels while the Assigned self-loop carries none, so 'reassign to a different staff member' reads as belonging to the wrong transition. All twelve transitions, their directions, authorised roles and guard conditions are otherwise correct.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR-011, FR-012, FR-013, NFR-005, RSK-05, SC-D-05, DEC-009, DEC-011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC-D-01, DEC-005, DEC-010, CON-03, RSK-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NFR-001, FR-022, FR-023, RSK-12, DEC-009, DEC-011</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-08</t>
@@ -4483,28 +4492,28 @@
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
     </row>
     <row r="6" customFormat="false" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10194,7 +10203,7 @@
         <v>564</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>565</v>
+        <v>973</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10240,7 +10249,7 @@
         <v>577</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>578</v>
+        <v>974</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10309,7 +10318,7 @@
         <v>597</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>598</v>
+        <v>975</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/docs/requirements/CivicConnect_M1_Registers.xlsx
+++ b/docs/requirements/CivicConnect_M1_Registers.xlsx
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="984">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="996">
   <si>
     <t xml:space="preserve">CivicConnect - Milestone 1 controlled registers</t>
   </si>
@@ -3040,6 +3040,42 @@
   </si>
   <si>
     <t xml:space="preserve">The assistant could not assess repository authenticity from a ZIP export alone (no .git history included) until the live repository URL was supplied; a snapshot without history can look complete while hiding whether the process was authentic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/PVY-Smit/civicconnect (public). Holds PED v1.0, the seventeen register sheets and both figures under docs/, with src/ and tests/ in place for M3.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ruleset "Protect main" (id 22248862), enforcement active on refs/heads/main: https://github.com/PVY-Smit/civicconnect/rules/22248862. bypass_actors is empty, so the control binds administrators as well. Read back from the GitHub API on 8 September 2026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/PVY-Smit/civicconnect/pulls?q=is%3Apr. Every change to a controlled artefact since the baseline commit has entered through a Pull Request: #18 AI Usage Register, #19 PED layout. The two direct commits to main predate the ruleset, which was created on 4 September 2026; none have occurred since.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ruleset rule pull_request, required_approving_review_count = 2: https://github.com/PVY-Smit/civicconnect/rules/22248862. GitHub does not permit an author to approve their own Pull Request, so self-approval cannot occur.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ruleset rule pull_request, dismiss_stale_reviews_on_push = true: https://github.com/PVY-Smit/civicconnect/rules/22248862. An approval therefore always refers to the commit that merges, not to an earlier one.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ruleset rules required_linear_history and non_fast_forward, both active: https://github.com/PVY-Smit/civicconnect/rules/22248862. Merge commits and force pushes to main are refused.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Convention in CONTRIBUTING.md, "Branch naming": https://github.com/PVY-Smit/civicconnect/blob/800b982f60ff7edb1931debc8525ffb6a48a5a20/CONTRIBUTING.md#L20-L26. Applied in the live branches docs/10-ai-register-js, docs/ped-layout-fix, docs/20-fec-decision-links and docs/6-governance-evidence.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Board: https://github.com/users/PVY-Smit/projects/1. Issues: https://github.com/PVY-Smit/civicconnect/issues. All eighteen issues are on the board, and each controlled change references its issue from the branch name and the Pull Request.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/PVY-Smit/civicconnect/blob/800b982f60ff7edb1931debc8525ffb6a48a5a20/.github/pull_request_template.md. In use on #18 and #19, both of which record the linked issue, the registers touched, the AI-assistance declaration and what the reviewer should focus on.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checklist in CONTRIBUTING.md, "Review checklist": https://github.com/PVY-Smit/civicconnect/blob/800b982f60ff7edb1931debc8525ffb6a48a5a20/CONTRIBUTING.md#L55-L68. NOT YET EVIDENCED: no review comment exists to link to. The control is configured but has not yet operated; the first review is due in review window 1 (#11). Left incomplete deliberately rather than pointed at the checklist text alone, because the criterion asks for evidence that the control operates, not that it is written down.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secret scanning and push protection both enabled, confirmed from the GitHub API on 8 September 2026: https://github.com/PVY-Smit/civicconnect/settings/security_analysis. Supported by .gitignore, which excludes .env, key and certificate files, and by .env.example, which carries placeholder values only (NFR-007, RSK-11).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/PVY-Smit/civicconnect/tree/main/docs. docs/PED, docs/requirements, docs/architecture, docs/decisions, docs/risk, docs/change, docs/quality, docs/security, docs/deployment, plus src/, tests/ and .github/. Folders for later milestones are present and empty by design (Master Brief, Appendix C).</t>
   </si>
 </sst>
 </file>
@@ -5468,8 +5504,8 @@
       <c r="B3" s="9" t="s">
         <v>879</v>
       </c>
-      <c r="C3" s="12" t="s">
-        <v>880</v>
+      <c r="C3" s="9" t="s">
+        <v>984</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5479,8 +5515,8 @@
       <c r="B4" s="10" t="s">
         <v>882</v>
       </c>
-      <c r="C4" s="12" t="s">
-        <v>883</v>
+      <c r="C4" s="10" t="s">
+        <v>985</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5490,8 +5526,8 @@
       <c r="B5" s="9" t="s">
         <v>885</v>
       </c>
-      <c r="C5" s="12" t="s">
-        <v>886</v>
+      <c r="C5" s="9" t="s">
+        <v>986</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5501,8 +5537,8 @@
       <c r="B6" s="10" t="s">
         <v>888</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>889</v>
+      <c r="C6" s="10" t="s">
+        <v>987</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5512,8 +5548,8 @@
       <c r="B7" s="9" t="s">
         <v>891</v>
       </c>
-      <c r="C7" s="12" t="s">
-        <v>892</v>
+      <c r="C7" s="9" t="s">
+        <v>988</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5523,8 +5559,8 @@
       <c r="B8" s="10" t="s">
         <v>894</v>
       </c>
-      <c r="C8" s="12" t="s">
-        <v>892</v>
+      <c r="C8" s="10" t="s">
+        <v>989</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5534,8 +5570,8 @@
       <c r="B9" s="9" t="s">
         <v>896</v>
       </c>
-      <c r="C9" s="12" t="s">
-        <v>897</v>
+      <c r="C9" s="9" t="s">
+        <v>990</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5545,8 +5581,8 @@
       <c r="B10" s="10" t="s">
         <v>899</v>
       </c>
-      <c r="C10" s="12" t="s">
-        <v>900</v>
+      <c r="C10" s="10" t="s">
+        <v>991</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5556,8 +5592,8 @@
       <c r="B11" s="9" t="s">
         <v>902</v>
       </c>
-      <c r="C11" s="12" t="s">
-        <v>903</v>
+      <c r="C11" s="9" t="s">
+        <v>992</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5568,7 +5604,7 @@
         <v>905</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>906</v>
+        <v>993</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5578,8 +5614,8 @@
       <c r="B13" s="9" t="s">
         <v>908</v>
       </c>
-      <c r="C13" s="12" t="s">
-        <v>892</v>
+      <c r="C13" s="9" t="s">
+        <v>994</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5589,8 +5625,8 @@
       <c r="B14" s="10" t="s">
         <v>910</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>911</v>
+      <c r="C14" s="10" t="s">
+        <v>995</v>
       </c>
     </row>
   </sheetData>

--- a/docs/requirements/CivicConnect_M1_Registers.xlsx
+++ b/docs/requirements/CivicConnect_M1_Registers.xlsx
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="996">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="997">
   <si>
     <t xml:space="preserve">CivicConnect - Milestone 1 controlled registers</t>
   </si>
@@ -3076,6 +3076,9 @@
   </si>
   <si>
     <t xml:space="preserve">https://github.com/PVY-Smit/civicconnect/tree/main/docs. docs/PED, docs/requirements, docs/architecture, docs/decisions, docs/risk, docs/change, docs/quality, docs/security, docs/deployment, plus src/, tests/ and .github/. Folders for later milestones are present and empty by design (Master Brief, Appendix C).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Board: https://github.com/users/PVY-Smit/projects/1. Issues: https://github.com/PVY-Smit/civicconnect/issues. Every issue raised on the project is placed on the board, and each controlled change references its issue from the branch name and from the Pull Request that implements it. No fixed count is stated here: the number changes whenever an issue is raised, and evidence that goes stale on its own is weaker than evidence that describes the control.</t>
   </si>
 </sst>
 </file>
@@ -5582,7 +5585,7 @@
         <v>899</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>991</v>
+        <v>996</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/docs/requirements/CivicConnect_M1_Registers.xlsx
+++ b/docs/requirements/CivicConnect_M1_Registers.xlsx
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="997">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="998">
   <si>
     <t xml:space="preserve">CivicConnect - Milestone 1 controlled registers</t>
   </si>
@@ -3079,6 +3079,9 @@
   </si>
   <si>
     <t xml:space="preserve">Board: https://github.com/users/PVY-Smit/projects/1. Issues: https://github.com/PVY-Smit/civicconnect/issues. Every issue raised on the project is placed on the board, and each controlled change references its issue from the branch name and from the Pull Request that implements it. No fixed count is stated here: the number changes whenever an issue is raised, and evidence that goes stale on its own is weaker than evidence that describes the control.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checklist in CONTRIBUTING.md, "Review checklist": https://github.com/PVY-Smit/civicconnect/blob/800b982f60ff7edb1931debc8525ffb6a48a5a20/CONTRIBUTING.md#L55-L68. The control operating, not merely configured: review of #18 found the registers-updated checklist inverted against the actual change, which was corrected in response (https://github.com/PVY-Smit/civicconnect/pull/18#issuecomment-5583144236); the same review found that the Figure 2 label defect was recorded in a register row but not tracked as work, and it was raised as issue #27 (https://github.com/PVY-Smit/civicconnect/pull/18#issuecomment-5583171255). Approval carrying reasoning rather than a bare tick: https://github.com/PVY-Smit/civicconnect/pull/19#pullrequestreview-5140293911.</t>
   </si>
 </sst>
 </file>
@@ -5606,8 +5609,8 @@
       <c r="B12" s="10" t="s">
         <v>905</v>
       </c>
-      <c r="C12" s="12" t="s">
-        <v>993</v>
+      <c r="C12" s="10" t="s">
+        <v>997</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/docs/requirements/CivicConnect_M1_Registers.xlsx
+++ b/docs/requirements/CivicConnect_M1_Registers.xlsx
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="998">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="999">
   <si>
     <t xml:space="preserve">CivicConnect - Milestone 1 controlled registers</t>
   </si>
@@ -3082,6 +3082,9 @@
   </si>
   <si>
     <t xml:space="preserve">Checklist in CONTRIBUTING.md, "Review checklist": https://github.com/PVY-Smit/civicconnect/blob/800b982f60ff7edb1931debc8525ffb6a48a5a20/CONTRIBUTING.md#L55-L68. The control operating, not merely configured: review of #18 found the registers-updated checklist inverted against the actual change, which was corrected in response (https://github.com/PVY-Smit/civicconnect/pull/18#issuecomment-5583144236); the same review found that the Figure 2 label defect was recorded in a register row but not tracked as work, and it was raised as issue #27 (https://github.com/PVY-Smit/civicconnect/pull/18#issuecomment-5583171255). Approval carrying reasoning rather than a bare tick: https://github.com/PVY-Smit/civicconnect/pull/19#pullrequestreview-5140293911.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The first attempt was rejected because it was not vector source that could be regenerated: the initial figure was a canvas rendering rather than SVG. It was redone as SVG generated from a Python script and rendered to PNG, so a marker can be moved by editing the source and re-rendering rather than by redrawing the image. Two discrepancies were then found on checking and are recorded rather than silently corrected. (1) Figure 1 names one gated decision per concern, but the Decision Log records FEC-01 and FEC-06 as gating DEC-009 as well as DEC-011, since DEC-009 requires the record-level authorisation shape from FEC-01 and the reporting load position from FEC-06; the figure understates those two rows by one decision. The Forward Considerations sheet also cites DEC-010 in the Links column for FEC-03 and FEC-05 but cites no decision for FEC-01 or FEC-06, so that link is recorded in the Decision Log only. (2) In Figure 2 the single New to In Progress arc carries two stacked labels while the Assigned self-loop carries none, so 'reassign to a different staff member' reads as belonging to the wrong transition; recorded as issue #27 and carried as a known limitation in s16.1 rather than corrected, since the diagram source is not held in the repository. All twelve transitions, their directions, authorised roles and guard conditions are otherwise correct.</t>
   </si>
 </sst>
 </file>
@@ -4607,7 +4610,7 @@
         <v>961</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>972</v>
+        <v>998</v>
       </c>
     </row>
     <row r="8" customFormat="false" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/docs/requirements/CivicConnect_M1_Registers.xlsx
+++ b/docs/requirements/CivicConnect_M1_Registers.xlsx
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="999">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="1013">
   <si>
     <t xml:space="preserve">CivicConnect - Milestone 1 controlled registers</t>
   </si>
@@ -3085,6 +3085,48 @@
   </si>
   <si>
     <t xml:space="preserve">The first attempt was rejected because it was not vector source that could be regenerated: the initial figure was a canvas rendering rather than SVG. It was redone as SVG generated from a Python script and rendered to PNG, so a marker can be moved by editing the source and re-rendering rather than by redrawing the image. Two discrepancies were then found on checking and are recorded rather than silently corrected. (1) Figure 1 names one gated decision per concern, but the Decision Log records FEC-01 and FEC-06 as gating DEC-009 as well as DEC-011, since DEC-009 requires the record-level authorisation shape from FEC-01 and the reporting load position from FEC-06; the figure understates those two rows by one decision. The Forward Considerations sheet also cites DEC-010 in the Links column for FEC-03 and FEC-05 but cites no decision for FEC-01 or FEC-06, so that link is recorded in the Decision Log only. (2) In Figure 2 the single New to In Progress arc carries two stacked labels while the Assigned self-loop carries none, so 'reassign to a different staff member' reads as belonging to the wrong transition; recorded as issue #27 and carried as a known limitation in s16.1 rather than corrected, since the diagram source is not held in the repository. All twelve transitions, their directions, authorised roles and guard conditions are otherwise correct.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tristan Roets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tristan Roets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Darius Mushi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jean Smit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tristan Roets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Darius Mushi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jean Smit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jean Smit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Darius Mushi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tristan Roets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jean Smit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Darius Mushi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tristan Roets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jean Smit</t>
   </si>
 </sst>
 </file>
@@ -9630,8 +9672,8 @@
       <c r="I3" s="9" t="s">
         <v>474</v>
       </c>
-      <c r="J3" s="12" t="s">
-        <v>475</v>
+      <c r="J3" s="9" t="s">
+        <v>999</v>
       </c>
       <c r="K3" s="9" t="s">
         <v>476</v>
@@ -9670,8 +9712,8 @@
       <c r="I4" s="10" t="s">
         <v>482</v>
       </c>
-      <c r="J4" s="12" t="s">
-        <v>483</v>
+      <c r="J4" s="10" t="s">
+        <v>1000</v>
       </c>
       <c r="K4" s="10" t="s">
         <v>476</v>
@@ -9710,8 +9752,8 @@
       <c r="I5" s="9" t="s">
         <v>488</v>
       </c>
-      <c r="J5" s="12" t="s">
-        <v>489</v>
+      <c r="J5" s="9" t="s">
+        <v>1001</v>
       </c>
       <c r="K5" s="9" t="s">
         <v>476</v>
@@ -9750,8 +9792,8 @@
       <c r="I6" s="10" t="s">
         <v>495</v>
       </c>
-      <c r="J6" s="12" t="s">
-        <v>475</v>
+      <c r="J6" s="10" t="s">
+        <v>1002</v>
       </c>
       <c r="K6" s="10" t="s">
         <v>476</v>
@@ -9790,8 +9832,8 @@
       <c r="I7" s="9" t="s">
         <v>500</v>
       </c>
-      <c r="J7" s="12" t="s">
-        <v>483</v>
+      <c r="J7" s="9" t="s">
+        <v>1003</v>
       </c>
       <c r="K7" s="9" t="s">
         <v>476</v>
@@ -9830,8 +9872,8 @@
       <c r="I8" s="10" t="s">
         <v>506</v>
       </c>
-      <c r="J8" s="12" t="s">
-        <v>489</v>
+      <c r="J8" s="10" t="s">
+        <v>1004</v>
       </c>
       <c r="K8" s="10" t="s">
         <v>476</v>
@@ -9870,8 +9912,8 @@
       <c r="I9" s="9" t="s">
         <v>512</v>
       </c>
-      <c r="J9" s="12" t="s">
-        <v>475</v>
+      <c r="J9" s="9" t="s">
+        <v>1005</v>
       </c>
       <c r="K9" s="9" t="s">
         <v>476</v>
@@ -9910,8 +9952,8 @@
       <c r="I10" s="10" t="s">
         <v>518</v>
       </c>
-      <c r="J10" s="12" t="s">
-        <v>483</v>
+      <c r="J10" s="10" t="s">
+        <v>1006</v>
       </c>
       <c r="K10" s="10" t="s">
         <v>476</v>
@@ -9950,8 +9992,8 @@
       <c r="I11" s="9" t="s">
         <v>523</v>
       </c>
-      <c r="J11" s="12" t="s">
-        <v>489</v>
+      <c r="J11" s="9" t="s">
+        <v>1007</v>
       </c>
       <c r="K11" s="9" t="s">
         <v>476</v>
@@ -9990,8 +10032,8 @@
       <c r="I12" s="10" t="s">
         <v>529</v>
       </c>
-      <c r="J12" s="12" t="s">
-        <v>483</v>
+      <c r="J12" s="10" t="s">
+        <v>1008</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>476</v>
@@ -10030,8 +10072,8 @@
       <c r="I13" s="9" t="s">
         <v>534</v>
       </c>
-      <c r="J13" s="12" t="s">
-        <v>475</v>
+      <c r="J13" s="9" t="s">
+        <v>1009</v>
       </c>
       <c r="K13" s="9" t="s">
         <v>476</v>
@@ -10070,8 +10112,8 @@
       <c r="I14" s="10" t="s">
         <v>540</v>
       </c>
-      <c r="J14" s="12" t="s">
-        <v>489</v>
+      <c r="J14" s="10" t="s">
+        <v>1010</v>
       </c>
       <c r="K14" s="10" t="s">
         <v>476</v>
@@ -10110,8 +10152,8 @@
       <c r="I15" s="9" t="s">
         <v>546</v>
       </c>
-      <c r="J15" s="12" t="s">
-        <v>483</v>
+      <c r="J15" s="9" t="s">
+        <v>1011</v>
       </c>
       <c r="K15" s="9" t="s">
         <v>476</v>
@@ -10150,8 +10192,8 @@
       <c r="I16" s="10" t="s">
         <v>552</v>
       </c>
-      <c r="J16" s="12" t="s">
-        <v>475</v>
+      <c r="J16" s="10" t="s">
+        <v>1012</v>
       </c>
       <c r="K16" s="10" t="s">
         <v>476</v>

--- a/docs/requirements/CivicConnect_M1_Registers.xlsx
+++ b/docs/requirements/CivicConnect_M1_Registers.xlsx
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="998">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="1013">
   <si>
     <t xml:space="preserve">CivicConnect - Milestone 1 controlled registers</t>
   </si>
@@ -3082,6 +3082,51 @@
   </si>
   <si>
     <t xml:space="preserve">Checklist in CONTRIBUTING.md, "Review checklist": https://github.com/PVY-Smit/civicconnect/blob/800b982f60ff7edb1931debc8525ffb6a48a5a20/CONTRIBUTING.md#L55-L68. The control operating, not merely configured: review of #18 found the registers-updated checklist inverted against the actual change, which was corrected in response (https://github.com/PVY-Smit/civicconnect/pull/18#issuecomment-5583144236); the same review found that the Figure 2 label defect was recorded in a register row but not tracked as work, and it was raised as issue #27 (https://github.com/PVY-Smit/civicconnect/pull/18#issuecomment-5583171255). Approval carrying reasoning rather than a bare tick: https://github.com/PVY-Smit/civicconnect/pull/19#pullrequestreview-5140293911.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tristan Roets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tristan Roets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Darius Mushi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jean Smit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tristan Roets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Darius Mushi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jean Smit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jean Smit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Darius Mushi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tristan Roets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jean Smit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Darius Mushi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tristan Roets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jean Smit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The first attempt was rejected because it was not vector source that could be regenerated: the initial figure was a canvas rendering rather than SVG. It was redone as SVG generated from a Python script and rendered to PNG, so a marker can be moved by editing the source and re-rendering rather than by redrawing the image. Two discrepancies were then found on checking and are recorded rather than silently corrected. (1) Figure 1 names one gated decision per concern, but the Decision Log records FEC-01 and FEC-06 as gating DEC-009 as well as DEC-011, since DEC-009 requires the record-level authorisation shape from FEC-01 and the reporting load position from FEC-06; the figure understates those two rows by one decision. The Forward Considerations sheet also cites DEC-010 in the Links column for FEC-03 and FEC-05 but cites no decision for FEC-01 or FEC-06, so that link is recorded in the Decision Log only. (2) In Figure 2 the single New to In Progress arc carries two stacked labels while the Assigned self-loop carries none, so 'reassign to a different staff member' reads as belonging to the wrong transition; recorded as issue #27 and carried as a known limitation in s16.1 rather than corrected, since the diagram source is not held in the repository. All twelve transitions, their directions, authorised roles and guard conditions are otherwise correct.</t>
   </si>
 </sst>
 </file>
@@ -4607,7 +4652,7 @@
         <v>961</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>972</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="8" customFormat="false" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9627,8 +9672,8 @@
       <c r="I3" s="9" t="s">
         <v>474</v>
       </c>
-      <c r="J3" s="12" t="s">
-        <v>475</v>
+      <c r="J3" s="9" t="s">
+        <v>998</v>
       </c>
       <c r="K3" s="9" t="s">
         <v>476</v>
@@ -9667,8 +9712,8 @@
       <c r="I4" s="10" t="s">
         <v>482</v>
       </c>
-      <c r="J4" s="12" t="s">
-        <v>483</v>
+      <c r="J4" s="10" t="s">
+        <v>999</v>
       </c>
       <c r="K4" s="10" t="s">
         <v>476</v>
@@ -9707,8 +9752,8 @@
       <c r="I5" s="9" t="s">
         <v>488</v>
       </c>
-      <c r="J5" s="12" t="s">
-        <v>489</v>
+      <c r="J5" s="9" t="s">
+        <v>1000</v>
       </c>
       <c r="K5" s="9" t="s">
         <v>476</v>
@@ -9747,8 +9792,8 @@
       <c r="I6" s="10" t="s">
         <v>495</v>
       </c>
-      <c r="J6" s="12" t="s">
-        <v>475</v>
+      <c r="J6" s="10" t="s">
+        <v>1001</v>
       </c>
       <c r="K6" s="10" t="s">
         <v>476</v>
@@ -9787,8 +9832,8 @@
       <c r="I7" s="9" t="s">
         <v>500</v>
       </c>
-      <c r="J7" s="12" t="s">
-        <v>483</v>
+      <c r="J7" s="9" t="s">
+        <v>1002</v>
       </c>
       <c r="K7" s="9" t="s">
         <v>476</v>
@@ -9827,8 +9872,8 @@
       <c r="I8" s="10" t="s">
         <v>506</v>
       </c>
-      <c r="J8" s="12" t="s">
-        <v>489</v>
+      <c r="J8" s="10" t="s">
+        <v>1003</v>
       </c>
       <c r="K8" s="10" t="s">
         <v>476</v>
@@ -9867,8 +9912,8 @@
       <c r="I9" s="9" t="s">
         <v>512</v>
       </c>
-      <c r="J9" s="12" t="s">
-        <v>475</v>
+      <c r="J9" s="9" t="s">
+        <v>1004</v>
       </c>
       <c r="K9" s="9" t="s">
         <v>476</v>
@@ -9907,8 +9952,8 @@
       <c r="I10" s="10" t="s">
         <v>518</v>
       </c>
-      <c r="J10" s="12" t="s">
-        <v>483</v>
+      <c r="J10" s="10" t="s">
+        <v>1005</v>
       </c>
       <c r="K10" s="10" t="s">
         <v>476</v>
@@ -9947,8 +9992,8 @@
       <c r="I11" s="9" t="s">
         <v>523</v>
       </c>
-      <c r="J11" s="12" t="s">
-        <v>489</v>
+      <c r="J11" s="9" t="s">
+        <v>1006</v>
       </c>
       <c r="K11" s="9" t="s">
         <v>476</v>
@@ -9987,8 +10032,8 @@
       <c r="I12" s="10" t="s">
         <v>529</v>
       </c>
-      <c r="J12" s="12" t="s">
-        <v>483</v>
+      <c r="J12" s="10" t="s">
+        <v>1007</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>476</v>
@@ -10027,8 +10072,8 @@
       <c r="I13" s="9" t="s">
         <v>534</v>
       </c>
-      <c r="J13" s="12" t="s">
-        <v>475</v>
+      <c r="J13" s="9" t="s">
+        <v>1008</v>
       </c>
       <c r="K13" s="9" t="s">
         <v>476</v>
@@ -10067,8 +10112,8 @@
       <c r="I14" s="10" t="s">
         <v>540</v>
       </c>
-      <c r="J14" s="12" t="s">
-        <v>489</v>
+      <c r="J14" s="10" t="s">
+        <v>1009</v>
       </c>
       <c r="K14" s="10" t="s">
         <v>476</v>
@@ -10107,8 +10152,8 @@
       <c r="I15" s="9" t="s">
         <v>546</v>
       </c>
-      <c r="J15" s="12" t="s">
-        <v>483</v>
+      <c r="J15" s="9" t="s">
+        <v>1010</v>
       </c>
       <c r="K15" s="9" t="s">
         <v>476</v>
@@ -10147,8 +10192,8 @@
       <c r="I16" s="10" t="s">
         <v>552</v>
       </c>
-      <c r="J16" s="12" t="s">
-        <v>475</v>
+      <c r="J16" s="10" t="s">
+        <v>1011</v>
       </c>
       <c r="K16" s="10" t="s">
         <v>476</v>

--- a/docs/requirements/CivicConnect_M1_Registers.xlsx
+++ b/docs/requirements/CivicConnect_M1_Registers.xlsx
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="1013">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="1021">
   <si>
     <t xml:space="preserve">CivicConnect - Milestone 1 controlled registers</t>
   </si>
@@ -3127,6 +3127,30 @@
   </si>
   <si>
     <t xml:space="preserve">The first attempt was rejected because it was not vector source that could be regenerated: the initial figure was a canvas rendering rather than SVG. It was redone as SVG generated from a Python script and rendered to PNG, so a marker can be moved by editing the source and re-rendering rather than by redrawing the image. Two discrepancies were then found on checking and are recorded rather than silently corrected. (1) Figure 1 names one gated decision per concern, but the Decision Log records FEC-01 and FEC-06 as gating DEC-009 as well as DEC-011, since DEC-009 requires the record-level authorisation shape from FEC-01 and the reporting load position from FEC-06; the figure understates those two rows by one decision. The Forward Considerations sheet also cites DEC-010 in the Links column for FEC-03 and FEC-05 but cites no decision for FEC-01 or FEC-06, so that link is recorded in the Decision Log only. (2) In Figure 2 the single New to In Progress arc carries two stacked labels while the Assigned self-loop carries none, so 'reassign to a different staff member' reads as belonging to the wrong transition; recorded as issue #27 and carried as a known limitation in s16.1 rather than corrected, since the diagram source is not held in the repository. All twelve transitions, their directions, authorised roles and guard conditions are otherwise correct.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tristan Roets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChatGPT (OpenAI, GPT-5.6 Sol)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reviewing M1 GitHub pull requests and preparing Risk Register and Forward Engineering Consideration evidence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assisted with identifying review blockers, checking traceability and governance issues, drafting review wording, and structuring Risk Register and FEC notes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compared the recommendations against the live GitHub pull requests, current main branch, CONTRIBUTING.md, issue requirements, and the controlled workbook and PED before accepting or revising them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accepted after revision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Some suggestions were based on incomplete or outdated repository state. These were rechecked against the live repository, corrected where necessary, and unsupported claims were rejected.</t>
   </si>
 </sst>
 </file>
@@ -4552,29 +4576,29 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="s">
-        <v>756</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>483</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>757</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>763</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>764</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>765</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>766</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>767</v>
+      <c r="A4" s="9" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>1018</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>1019</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>1020</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/docs/requirements/CivicConnect_M1_Registers.xlsx
+++ b/docs/requirements/CivicConnect_M1_Registers.xlsx
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="1013">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="1025">
   <si>
     <t xml:space="preserve">CivicConnect - Milestone 1 controlled registers</t>
   </si>
@@ -3127,6 +3127,42 @@
   </si>
   <si>
     <t xml:space="preserve">The first attempt was rejected because it was not vector source that could be regenerated: the initial figure was a canvas rendering rather than SVG. It was redone as SVG generated from a Python script and rendered to PNG, so a marker can be moved by editing the source and re-rendering rather than by redrawing the image. Two discrepancies were then found on checking and are recorded rather than silently corrected. (1) Figure 1 names one gated decision per concern, but the Decision Log records FEC-01 and FEC-06 as gating DEC-009 as well as DEC-011, since DEC-009 requires the record-level authorisation shape from FEC-01 and the reporting load position from FEC-06; the figure understates those two rows by one decision. The Forward Considerations sheet also cites DEC-010 in the Links column for FEC-03 and FEC-05 but cites no decision for FEC-01 or FEC-06, so that link is recorded in the Decision Log only. (2) In Figure 2 the single New to In Progress arc carries two stacked labels while the Assigned self-loop carries none, so 'reassign to a different staff member' reads as belonging to the wrong transition; recorded as issue #27 and carried as a known limitation in s16.1 rather than corrected, since the diagram source is not held in the repository. All twelve transitions, their directions, authorised roles and guard conditions are otherwise correct.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materialised - active (review delay recorded 9 September 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CON-08, FEC-07, #11, PR #18, PR #19, PR #31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materialised - active (member availability affected M1 review capacity on 9 September 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CON-02, CON-06, CON-08, FEC-07, #11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RSK-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A controlled engineering artefact cannot be safely reproduced or corrected because only the rendered output is retained.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generated diagrams or similar artefacts are committed without their editable source or generation script.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commit editable source or generation scripts alongside generated artefacts, and regenerate and compare outputs against the authoritative register.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Record the limitation, reconstruct the source, and independently verify the replacement against the controlled evidence before accepting it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jean Smit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materialised - Figure 2, issue #27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#27, PED s16.1, Status Model sheet, Figure 2, #36</t>
   </si>
 </sst>
 </file>
@@ -9574,7 +9610,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -9796,10 +9832,10 @@
         <v>1001</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>476</v>
+        <v>1013</v>
       </c>
       <c r="L6" s="10" t="s">
-        <v>496</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9893,7 +9929,7 @@
         <v>510</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" s="9" t="n">
         <v>4</v>
@@ -9916,10 +9952,10 @@
         <v>1004</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>476</v>
+        <v>1015</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>513</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10200,6 +10236,44 @@
       </c>
       <c r="L16" s="10" t="s">
         <v>553</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="9" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D17" s="9">
+        <v>3</v>
+      </c>
+      <c r="E17" s="9">
+        <v>3</v>
+      </c>
+      <c r="F17" s="9">
+        <f>D17*E17</f>
+      </c>
+      <c r="G17" s="9">
+        <f>IF(F17&gt;=20,"Critical",IF(F17&gt;=12,"High",IF(F17&gt;=6,"Medium","Low")))</f>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>1021</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>1022</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>1023</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>1024</v>
       </c>
     </row>
   </sheetData>

--- a/docs/requirements/CivicConnect_M1_Registers.xlsx
+++ b/docs/requirements/CivicConnect_M1_Registers.xlsx
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="1013">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="1016">
   <si>
     <t xml:space="preserve">CivicConnect - Milestone 1 controlled registers</t>
   </si>
@@ -3127,6 +3127,15 @@
   </si>
   <si>
     <t xml:space="preserve">The first attempt was rejected because it was not vector source that could be regenerated: the initial figure was a canvas rendering rather than SVG. It was redone as SVG generated from a Python script and rendered to PNG, so a marker can be moved by editing the source and re-rendering rather than by redrawing the image. Two discrepancies were then found on checking and are recorded rather than silently corrected. (1) Figure 1 names one gated decision per concern, but the Decision Log records FEC-01 and FEC-06 as gating DEC-009 as well as DEC-011, since DEC-009 requires the record-level authorisation shape from FEC-01 and the reporting load position from FEC-06; the figure understates those two rows by one decision. The Forward Considerations sheet also cites DEC-010 in the Links column for FEC-03 and FEC-05 but cites no decision for FEC-01 or FEC-06, so that link is recorded in the Decision Log only. (2) In Figure 2 the single New to In Progress arc carries two stacked labels while the Assigned self-loop carries none, so 'reassign to a different staff member' reads as belonging to the wrong transition; recorded as issue #27 and carried as a known limitation in s16.1 rather than corrected, since the diagram source is not held in the repository. All twelve transitions, their directions, authorised roles and guard conditions are otherwise correct.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Team approval - Jean Smit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Team approval - Tristan Roets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Team approval - Darius Mushi</t>
   </si>
 </sst>
 </file>
@@ -5828,7 +5837,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>934</v>
+        <v>1013</v>
       </c>
       <c r="B16" s="10" t="s">
         <v>935</v>
@@ -5836,7 +5845,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>936</v>
+        <v>1014</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>935</v>
@@ -5844,7 +5853,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>937</v>
+        <v>1015</v>
       </c>
       <c r="B18" s="10" t="s">
         <v>935</v>

--- a/docs/requirements/CivicConnect_M1_Registers.xlsx
+++ b/docs/requirements/CivicConnect_M1_Registers.xlsx
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="1021">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1761" uniqueCount="1036">
   <si>
     <t xml:space="preserve">CivicConnect - Milestone 1 controlled registers</t>
   </si>
@@ -3151,6 +3151,51 @@
   </si>
   <si>
     <t xml:space="preserve">Some suggestions were based on incomplete or outdated repository state. These were rechecked against the live repository, corrected where necessary, and unsupported claims were rejected.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materialised - active (review delay recorded 9 September 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CON-08, FEC-07, #11, PR #18, PR #19, PR #31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materialised - active (member availability affected M1 review capacity on 9 September 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CON-02, CON-06, CON-08, FEC-07, #11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RSK-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A controlled engineering artefact cannot be safely reproduced or corrected because only the rendered output is retained.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generated diagrams or similar artefacts are committed without their editable source or generation script.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commit editable source or generation scripts alongside generated artefacts, and regenerate and compare outputs against the authoritative register.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Record the limitation, reconstruct the source, and independently verify the replacement against the controlled evidence before accepting it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jean Smit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materialised - Figure 2, issue #27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#27, PED s16.1, Status Model sheet, Figure 2, #36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Team approval - Jean Smit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Team approval - Tristan Roets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Team approval - Darius Mushi</t>
   </si>
 </sst>
 </file>
@@ -5852,7 +5897,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>934</v>
+        <v>1033</v>
       </c>
       <c r="B16" s="10" t="s">
         <v>935</v>
@@ -5860,7 +5905,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>936</v>
+        <v>1034</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>935</v>
@@ -5868,7 +5913,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>937</v>
+        <v>1035</v>
       </c>
       <c r="B18" s="10" t="s">
         <v>935</v>
@@ -9598,7 +9643,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -9820,10 +9865,10 @@
         <v>1001</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>476</v>
+        <v>1021</v>
       </c>
       <c r="L6" s="10" t="s">
-        <v>496</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9917,7 +9962,7 @@
         <v>510</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" s="9" t="n">
         <v>4</v>
@@ -9940,10 +9985,10 @@
         <v>1004</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>476</v>
+        <v>1023</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>513</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10224,6 +10269,44 @@
       </c>
       <c r="L16" s="10" t="s">
         <v>553</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="9" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D17" s="9">
+        <v>3</v>
+      </c>
+      <c r="E17" s="9">
+        <v>3</v>
+      </c>
+      <c r="F17" s="9">
+        <f>D17*E17</f>
+      </c>
+      <c r="G17" s="9">
+        <f>IF(F17&gt;=20,"Critical",IF(F17&gt;=12,"High",IF(F17&gt;=6,"Medium","Low")))</f>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>1028</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>1029</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>1030</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>1031</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>1032</v>
       </c>
     </row>
   </sheetData>
